--- a/business_surveys/047_vendor_invoice_experience_survey--business_surveys.xlsx
+++ b/business_surveys/047_vendor_invoice_experience_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Bank Transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'in_person',_'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'In Person', 'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'weekly',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Weekly', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'bi-weekly',_'label':_'bi-weekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Bi-Weekly', 'label': 'Bi-Weekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'monthly',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Monthly', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'quarterly',_'label':_'quarterly'}</t>
+          <t>quarterly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Quarterly', 'label': 'Quarterly'}</t>
+          <t>Quarterly</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'annually',_'label':_'annually'}</t>
+          <t>annually</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Annually', 'label': 'Annually'}</t>
+          <t>Annually</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'on_demand',_'label':_'on_demand'}</t>
+          <t>on_demand</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'On Demand', 'label': 'On Demand'}</t>
+          <t>On Demand</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'once',_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Once', 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'reoccurring',_'label':_'reoccurring'}</t>
+          <t>reoccurring</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Reoccurring', 'label': 'Reoccurring'}</t>
+          <t>Reoccurring</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'on_demand',_'label':_'on_demand'}</t>
+          <t>on_demand</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'On Demand', 'label': 'On Demand'}</t>
+          <t>On Demand</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'bank_transfer',_'label':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Bank Transfer', 'label': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'check',_'label':_'check'}</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Check', 'label': 'Check'}</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'online_transfer',_'label':_'online_transfer'}</t>
+          <t>online_transfer</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Online Transfer', 'label': 'Online Transfer'}</t>
+          <t>Online Transfer</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'paid',_'label':_'paid'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Paid', 'label': 'Paid'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'unpaid',_'label':_'unpaid'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Unpaid', 'label': 'Unpaid'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'partially_paid',_'label':_'partially_paid'}</t>
+          <t>partially_paid</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Partially Paid', 'label': 'Partially Paid'}</t>
+          <t>Partially Paid</t>
         </is>
       </c>
     </row>
